--- a/График выпуска спектакля молодожены.xlsx
+++ b/График выпуска спектакля молодожены.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Тимонин\График выпуска сУРСУЛА\График выпуска спектакля\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\СТРУКТУРА ХПЧ МХАТ\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>Сценические репетиции на сценической площадке в полном оформлении, прогоны.</t>
   </si>
@@ -68,12 +68,6 @@
     <t>Презентация макета художественного оформления спектакля и его утверждение.</t>
   </si>
   <si>
-    <t>10-20</t>
-  </si>
-  <si>
-    <t>20-31</t>
-  </si>
-  <si>
     <t>Презентация концепции Проекта сценографического искусства на уровне предварительных эскизов, прирезок к макету.</t>
   </si>
   <si>
@@ -89,9 +83,6 @@
     <t>Дни  премьерных показов.</t>
   </si>
   <si>
-    <t>3-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">Технологическая разработка художественно-постановочной частью материалов Проекта сценографического искусства. Формирование технического задания для мастерских.  </t>
   </si>
   <si>
@@ -150,15 +141,6 @@
   </si>
   <si>
     <t xml:space="preserve">КАЛЕНДАРНЫЙ ПЛАН РАБОТ ПО  ВЫПУСКУ  СПЕКТАКЛЯ "Молодожены" </t>
-  </si>
-  <si>
-    <t>Апрель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Март </t>
-  </si>
-  <si>
-    <t>20-30</t>
   </si>
   <si>
     <t>Ответсвенное лицо: ФИО</t>
@@ -281,7 +263,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,6 +365,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -793,7 +781,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -959,23 +947,7 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1072,39 +1044,49 @@
     <xf numFmtId="49" fontId="6" fillId="11" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="11" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="25" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="25" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="25" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="25" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="11" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Название" xfId="1" builtinId="15"/>
@@ -1430,7 +1412,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AE27"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -1450,288 +1432,256 @@
     <col min="19" max="19" width="5.125" customWidth="1"/>
     <col min="20" max="20" width="4.5" customWidth="1"/>
     <col min="21" max="21" width="5.375" customWidth="1"/>
-    <col min="22" max="22" width="4" customWidth="1"/>
-    <col min="23" max="23" width="3.875" customWidth="1"/>
-    <col min="24" max="25" width="3.5" customWidth="1"/>
-    <col min="26" max="26" width="3.375" customWidth="1"/>
-    <col min="27" max="27" width="3" customWidth="1"/>
-    <col min="28" max="29" width="3.375" customWidth="1"/>
-    <col min="30" max="31" width="3" customWidth="1"/>
+    <col min="22" max="22" width="5.875" customWidth="1"/>
+    <col min="23" max="23" width="6.625" customWidth="1"/>
+    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="25" max="25" width="6.625" customWidth="1"/>
+    <col min="26" max="26" width="8.875" customWidth="1"/>
+    <col min="27" max="28" width="8.625" customWidth="1"/>
+    <col min="29" max="29" width="10.875" customWidth="1"/>
+    <col min="30" max="30" width="28.5" customWidth="1"/>
+    <col min="31" max="31" width="3" customWidth="1"/>
     <col min="32" max="34" width="6" customWidth="1"/>
     <col min="35" max="35" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108"/>
-      <c r="AA1" s="108"/>
-      <c r="AB1" s="108"/>
-      <c r="AC1" s="108"/>
-      <c r="AD1" s="108"/>
-      <c r="AE1" s="108"/>
-    </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+    <row r="1" spans="1:31" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="102" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="103"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
+      <c r="Z1" s="103"/>
+      <c r="AA1" s="103"/>
+      <c r="AB1" s="103"/>
+      <c r="AC1" s="103"/>
+      <c r="AD1" s="103"/>
+      <c r="AE1" s="103"/>
+    </row>
+    <row r="2" spans="1:31" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="104" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="104" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="104" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="104" t="s">
+      <c r="B2" s="100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="100" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="100" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="101"/>
+      <c r="T2" s="101"/>
+      <c r="U2" s="101"/>
+      <c r="V2" s="101"/>
+      <c r="W2" s="101"/>
+      <c r="X2" s="101"/>
+      <c r="Y2" s="101"/>
+      <c r="Z2" s="101"/>
+      <c r="AA2" s="100" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB2" s="101"/>
+      <c r="AC2" s="101"/>
+    </row>
+    <row r="3" spans="1:31" s="19" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="104"/>
+      <c r="B3" s="92" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="92" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="95" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="94" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="93">
+        <v>23</v>
+      </c>
+      <c r="S3" s="93">
+        <v>24</v>
+      </c>
+      <c r="T3" s="93">
+        <v>25</v>
+      </c>
+      <c r="U3" s="93">
+        <v>26</v>
+      </c>
+      <c r="V3" s="92">
+        <v>27</v>
+      </c>
+      <c r="W3" s="92">
+        <v>28</v>
+      </c>
+      <c r="X3" s="92">
+        <v>29</v>
+      </c>
+      <c r="Y3" s="92">
+        <v>30</v>
+      </c>
+      <c r="Z3" s="92" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA3" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB3" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC3" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD3" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="104"/>
-      <c r="O2" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="104" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105"/>
-      <c r="V2" s="105"/>
-      <c r="W2" s="105"/>
-      <c r="X2" s="105"/>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="105"/>
-      <c r="AA2" s="105"/>
-      <c r="AB2" s="105"/>
-      <c r="AC2" s="105"/>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="105"/>
-      <c r="AF2" s="104" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG2" s="105"/>
-      <c r="AH2" s="105"/>
-    </row>
-    <row r="3" spans="1:35" s="19" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="109"/>
-      <c r="B3" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="100" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="100" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="100" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="100" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="100" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="100" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="102" t="s">
-        <v>4</v>
-      </c>
-      <c r="N3" s="103" t="s">
-        <v>7</v>
-      </c>
-      <c r="O3" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="P3" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="102" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="100" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="U3" s="102" t="s">
-        <v>4</v>
-      </c>
-      <c r="V3" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="W3" s="101">
-        <v>23</v>
-      </c>
-      <c r="X3" s="101">
-        <v>24</v>
-      </c>
-      <c r="Y3" s="101">
-        <v>25</v>
-      </c>
-      <c r="Z3" s="101">
-        <v>26</v>
-      </c>
-      <c r="AA3" s="100">
-        <v>27</v>
-      </c>
-      <c r="AB3" s="100">
-        <v>28</v>
-      </c>
-      <c r="AC3" s="100">
-        <v>29</v>
-      </c>
-      <c r="AD3" s="100">
-        <v>30</v>
-      </c>
-      <c r="AE3" s="100" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF3" s="102" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG3" s="102" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH3" s="102" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI3" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="43" t="s">
-        <v>20</v>
-      </c>
       <c r="B4" s="24"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="24"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="28"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="25"/>
       <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="28"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
       <c r="T4" s="25"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="54"/>
-      <c r="AI4" s="13"/>
-    </row>
-    <row r="5" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U4" s="25"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="13"/>
+    </row>
+    <row r="5" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="57" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="5"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="3"/>
       <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="5"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="58"/>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
-    </row>
-    <row r="6" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U5" s="3"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="48"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="58"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+    </row>
+    <row r="6" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="62" t="s">
         <v>0</v>
       </c>
@@ -1754,23 +1704,18 @@
       <c r="R6" s="13"/>
       <c r="S6" s="12"/>
       <c r="T6" s="6"/>
-      <c r="U6" s="63"/>
-      <c r="V6" s="64"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="68"/>
-      <c r="AE6" s="69"/>
-      <c r="AF6" s="70"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="4"/>
-      <c r="AI6" s="4"/>
-    </row>
-    <row r="7" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U6" s="7"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="107"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+    </row>
+    <row r="7" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="60" t="s">
         <v>6</v>
       </c>
@@ -1793,24 +1738,19 @@
       <c r="R7" s="13"/>
       <c r="S7" s="12"/>
       <c r="T7" s="6"/>
-      <c r="U7" s="71"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="49"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="3"/>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
-    </row>
-    <row r="8" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="73" t="s">
+      <c r="U7" s="7"/>
+      <c r="V7" s="109"/>
+      <c r="W7" s="110"/>
+      <c r="X7" s="110"/>
+      <c r="Y7" s="111"/>
+      <c r="Z7" s="112"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+    </row>
+    <row r="8" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="65" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2"/>
@@ -1832,25 +1772,20 @@
       <c r="R8" s="13"/>
       <c r="S8" s="12"/>
       <c r="T8" s="6"/>
-      <c r="U8" s="74"/>
+      <c r="U8" s="66"/>
       <c r="V8" s="8"/>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="11"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="49"/>
-      <c r="AF8" s="2"/>
-      <c r="AG8" s="3"/>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
-    </row>
-    <row r="9" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="75" t="s">
-        <v>33</v>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="49"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+    </row>
+    <row r="9" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="67" t="s">
+        <v>30</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="13"/>
@@ -1875,19 +1810,14 @@
       <c r="V9" s="8"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="13"/>
-    </row>
-    <row r="10" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+    </row>
+    <row r="10" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61" t="s">
         <v>10</v>
       </c>
@@ -1904,31 +1834,26 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="14"/>
-      <c r="O10" s="76"/>
-      <c r="P10" s="77"/>
-      <c r="Q10" s="77"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="79"/>
-      <c r="T10" s="77"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="69"/>
       <c r="U10" s="7"/>
       <c r="V10" s="8"/>
       <c r="W10" s="6"/>
       <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="49"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="3"/>
-      <c r="AH10" s="4"/>
-      <c r="AI10" s="4"/>
-    </row>
-    <row r="11" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="49"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+    </row>
+    <row r="11" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4"/>
@@ -1943,31 +1868,26 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="14"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="78"/>
-      <c r="S11" s="79"/>
-      <c r="T11" s="77"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="69"/>
       <c r="U11" s="7"/>
       <c r="V11" s="8"/>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="49"/>
-      <c r="AF11" s="2"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="4"/>
-      <c r="AI11" s="4"/>
-    </row>
-    <row r="12" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="72" t="s">
-        <v>31</v>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+    </row>
+    <row r="12" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="64" t="s">
+        <v>28</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="13"/>
@@ -1980,8 +1900,8 @@
       <c r="J12" s="13"/>
       <c r="K12" s="5"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="80"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
       <c r="O12" s="8"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1992,34 +1912,29 @@
       <c r="V12" s="8"/>
       <c r="W12" s="6"/>
       <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-    </row>
-    <row r="13" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="85"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+    </row>
+    <row r="13" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="77"/>
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
       <c r="P13" s="6"/>
@@ -2031,21 +1946,16 @@
       <c r="V13" s="8"/>
       <c r="W13" s="6"/>
       <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="49"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="13"/>
-    </row>
-    <row r="14" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+    </row>
+    <row r="14" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="13"/>
@@ -2070,21 +1980,16 @@
       <c r="V14" s="8"/>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="49"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="6"/>
-      <c r="AH14" s="13"/>
-      <c r="AI14" s="13"/>
-    </row>
-    <row r="15" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="49"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="13"/>
+    </row>
+    <row r="15" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="13"/>
@@ -2109,21 +2014,16 @@
       <c r="V15" s="2"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="49"/>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="13"/>
-    </row>
-    <row r="16" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="13"/>
+      <c r="AD15" s="13"/>
+    </row>
+    <row r="16" spans="1:31" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="46" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="13"/>
@@ -2148,27 +2048,22 @@
       <c r="V16" s="2"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="49"/>
-      <c r="AF16" s="8"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="13"/>
-      <c r="AI16" s="13"/>
-    </row>
-    <row r="17" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="72" t="s">
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="49"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="13"/>
+      <c r="AD16" s="13"/>
+    </row>
+    <row r="17" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="87"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="54"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="72"/>
       <c r="G17" s="8"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
@@ -2187,66 +2082,56 @@
       <c r="V17" s="2"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="11"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="49"/>
-      <c r="AF17" s="8"/>
-      <c r="AG17" s="6"/>
-      <c r="AH17" s="13"/>
-      <c r="AI17" s="13"/>
-    </row>
-    <row r="18" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="49"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+    </row>
+    <row r="18" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="76"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="90"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="77"/>
-      <c r="M18" s="77"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="76"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="77"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="79"/>
-      <c r="T18" s="77"/>
+        <v>22</v>
+      </c>
+      <c r="B18" s="68"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="70"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="69"/>
       <c r="U18" s="14"/>
       <c r="V18" s="2"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="49"/>
-      <c r="AF18" s="8"/>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="13"/>
-      <c r="AI18" s="13"/>
-    </row>
-    <row r="19" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+    </row>
+    <row r="19" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="59" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="13"/>
       <c r="D19" s="12"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="92"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="84"/>
       <c r="G19" s="8"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
@@ -2265,26 +2150,21 @@
       <c r="V19" s="2"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="49"/>
-      <c r="AF19" s="8"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="13"/>
-      <c r="AI19" s="13"/>
-    </row>
-    <row r="20" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="72" t="s">
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="49"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+    </row>
+    <row r="20" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="64" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="89"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
       <c r="H20" s="6"/>
@@ -2304,25 +2184,20 @@
       <c r="V20" s="2"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="49"/>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="13"/>
-      <c r="AI20" s="13"/>
-    </row>
-    <row r="21" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+    </row>
+    <row r="21" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21" s="8"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="86"/>
       <c r="E21" s="6"/>
       <c r="F21" s="9"/>
       <c r="G21" s="8"/>
@@ -2343,25 +2218,20 @@
       <c r="V21" s="2"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="11"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="49"/>
-      <c r="AF21" s="8"/>
-      <c r="AG21" s="6"/>
-      <c r="AH21" s="20"/>
-      <c r="AI21" s="20"/>
-    </row>
-    <row r="22" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="96"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+    </row>
+    <row r="22" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="88"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="12"/>
       <c r="F22" s="9"/>
       <c r="G22" s="8"/>
@@ -2382,26 +2252,21 @@
       <c r="V22" s="5"/>
       <c r="W22" s="3"/>
       <c r="X22" s="14"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="11"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="49"/>
-      <c r="AF22" s="8"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="20"/>
-      <c r="AI22" s="20"/>
-    </row>
-    <row r="23" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="87"/>
-      <c r="E23" s="88"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="49"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="20"/>
+    </row>
+    <row r="23" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="79"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="13"/>
       <c r="G23" s="8"/>
       <c r="H23" s="6"/>
@@ -2421,23 +2286,18 @@
       <c r="V23" s="5"/>
       <c r="W23" s="3"/>
       <c r="X23" s="14"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="49"/>
-      <c r="AF23" s="8"/>
-      <c r="AG23" s="6"/>
-      <c r="AH23" s="13"/>
-      <c r="AI23" s="13"/>
-    </row>
-    <row r="24" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="8"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+    </row>
+    <row r="24" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="95"/>
+        <v>24</v>
+      </c>
+      <c r="B24" s="87"/>
       <c r="C24" s="40"/>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
@@ -2460,23 +2320,18 @@
       <c r="V24" s="5"/>
       <c r="W24" s="3"/>
       <c r="X24" s="14"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="11"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="11"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="49"/>
-      <c r="AF24" s="8"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="13"/>
-      <c r="AI24" s="13"/>
-    </row>
-    <row r="25" spans="1:35" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="49"/>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+    </row>
+    <row r="25" spans="1:30" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="99"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="91"/>
       <c r="C25" s="42"/>
       <c r="D25" s="33"/>
       <c r="E25" s="33"/>
@@ -2499,197 +2354,164 @@
       <c r="V25" s="29"/>
       <c r="W25" s="16"/>
       <c r="X25" s="17"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="56"/>
-      <c r="AF25" s="8"/>
-      <c r="AG25" s="6"/>
-      <c r="AH25" s="13"/>
-      <c r="AI25" s="112"/>
-    </row>
-    <row r="26" spans="1:35" s="19" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="109" t="s">
+      <c r="Y25" s="18"/>
+      <c r="Z25" s="56"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="13"/>
+      <c r="AD25" s="97"/>
+    </row>
+    <row r="26" spans="1:30" s="19" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="104" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="104" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="104" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="104" t="s">
-        <v>18</v>
-      </c>
-      <c r="L26" s="104"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="106" t="s">
+      <c r="B26" s="100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="100" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="105"/>
+      <c r="L26" s="105"/>
+      <c r="M26" s="105"/>
+      <c r="N26" s="100" t="s">
+        <v>33</v>
+      </c>
+      <c r="O26" s="101"/>
+      <c r="P26" s="101"/>
+      <c r="Q26" s="101"/>
+      <c r="R26" s="101"/>
+      <c r="S26" s="101"/>
+      <c r="T26" s="101"/>
+      <c r="U26" s="101"/>
+      <c r="V26" s="101"/>
+      <c r="W26" s="101"/>
+      <c r="X26" s="101"/>
+      <c r="Y26" s="101"/>
+      <c r="Z26" s="101"/>
+      <c r="AA26" s="100" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB26" s="101"/>
+      <c r="AC26" s="106"/>
+      <c r="AD26" s="98" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="104"/>
+      <c r="B27" s="92" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="92" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="95" t="s">
+        <v>7</v>
+      </c>
+      <c r="J27" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="O27" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="94" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="93">
+        <v>23</v>
+      </c>
+      <c r="S27" s="93">
+        <v>24</v>
+      </c>
+      <c r="T27" s="93">
+        <v>25</v>
+      </c>
+      <c r="U27" s="93">
+        <v>26</v>
+      </c>
+      <c r="V27" s="92">
+        <v>27</v>
+      </c>
+      <c r="W27" s="92">
+        <v>28</v>
+      </c>
+      <c r="X27" s="92">
+        <v>29</v>
+      </c>
+      <c r="Y27" s="92">
+        <v>30</v>
+      </c>
+      <c r="Z27" s="92" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA27" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB27" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC27" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="P26" s="106"/>
-      <c r="Q26" s="106"/>
-      <c r="R26" s="106"/>
-      <c r="S26" s="104" t="s">
-        <v>36</v>
-      </c>
-      <c r="T26" s="105"/>
-      <c r="U26" s="105"/>
-      <c r="V26" s="105"/>
-      <c r="W26" s="105"/>
-      <c r="X26" s="105"/>
-      <c r="Y26" s="105"/>
-      <c r="Z26" s="105"/>
-      <c r="AA26" s="105"/>
-      <c r="AB26" s="105"/>
-      <c r="AC26" s="105"/>
-      <c r="AD26" s="105"/>
-      <c r="AE26" s="105"/>
-      <c r="AF26" s="104" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG26" s="105"/>
-      <c r="AH26" s="110"/>
-      <c r="AI26" s="113" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="109"/>
-      <c r="B27" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="100" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="100" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="100" t="s">
-        <v>44</v>
-      </c>
-      <c r="G27" s="100" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="100" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="100" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="L27" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="102" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="103" t="s">
-        <v>7</v>
-      </c>
-      <c r="O27" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="P27" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="102" t="s">
-        <v>4</v>
-      </c>
-      <c r="R27" s="100" t="s">
-        <v>8</v>
-      </c>
-      <c r="S27" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="T27" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="102" t="s">
-        <v>4</v>
-      </c>
-      <c r="V27" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="101">
-        <v>23</v>
-      </c>
-      <c r="X27" s="101">
-        <v>24</v>
-      </c>
-      <c r="Y27" s="101">
-        <v>25</v>
-      </c>
-      <c r="Z27" s="101">
-        <v>26</v>
-      </c>
-      <c r="AA27" s="100">
-        <v>27</v>
-      </c>
-      <c r="AB27" s="100">
-        <v>28</v>
-      </c>
-      <c r="AC27" s="100">
-        <v>29</v>
-      </c>
-      <c r="AD27" s="100">
-        <v>30</v>
-      </c>
-      <c r="AE27" s="100" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF27" s="102" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG27" s="102" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH27" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI27" s="114" t="s">
-        <v>47</v>
+      <c r="AD27" s="99" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="AF2:AH2"/>
+  <mergeCells count="13">
+    <mergeCell ref="AA26:AC26"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="S2:AE2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="S26:AE26"/>
-    <mergeCell ref="AF26:AH26"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="N2:Z2"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="N26:Z26"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
